--- a/Zaeem Zahid Kahoot.xlsx
+++ b/Zaeem Zahid Kahoot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zaeem\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C604B0CB-FE86-4CF1-BC24-A87FD2BEC042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DECD3063-5289-4E2C-99D8-CD9CCC4AB324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="338" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,9 +70,6 @@
     <t>To automatically generate method implementations.</t>
   </si>
   <si>
-    <t>To automatically generate method implementations based on the class's attributes and predefined logic.</t>
-  </si>
-  <si>
     <t>In a JUNIT test, what color signfies a test case that failed.</t>
   </si>
   <si>
@@ -106,16 +103,19 @@
     <t>To reduce the visibility of a method from public to private in the subclass.</t>
   </si>
   <si>
-    <t>To allow a class to inherit multiple methods with the same name from different classes.</t>
+    <t>java.exc.Exception</t>
   </si>
   <si>
-    <t>To change the return type of a method to a different data type.</t>
+    <t>Inherits multiple methods with the same name from different classes</t>
   </si>
   <si>
-    <t>To provide a specific implementation of a method pre-defined in a parent class.</t>
+    <t>To change the return type of a method to a different data type</t>
   </si>
   <si>
-    <t>java.exc.Exception</t>
+    <t>To give a specific implementation for method pre-defined in a parent class</t>
+  </si>
+  <si>
+    <t>To automatically generate method based on the class's predefined logic</t>
   </si>
 </sst>
 </file>
@@ -281,116 +281,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <sz val="10"/>
@@ -1016,15 +918,15 @@
     </row>
     <row r="3" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1047,15 +949,15 @@
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1109,15 +1011,15 @@
     </row>
     <row r="6" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1212,25 +1114,25 @@
     </row>
     <row r="9" spans="1:27" ht="75" x14ac:dyDescent="0.35">
       <c r="A9" s="11"/>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="20">
         <v>10</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="20">
         <v>4</v>
       </c>
       <c r="I9" s="1"/>
@@ -1255,25 +1157,25 @@
     </row>
     <row r="10" spans="1:27" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A10" s="11"/>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="D10" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="E10" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="22">
+      <c r="F10" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="20">
         <v>10</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="20">
         <v>3</v>
       </c>
       <c r="I10" s="1"/>
@@ -1296,29 +1198,29 @@
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
     </row>
-    <row r="11" spans="1:27" ht="93.75" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:27" ht="75" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
         <v>2</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="22">
+      <c r="F11" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="20">
         <v>10</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="20">
         <v>3</v>
       </c>
       <c r="I11" s="1"/>
@@ -1345,25 +1247,25 @@
       <c r="A12" s="11">
         <v>3</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="D12" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="E12" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="F12" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="22">
+      <c r="G12" s="20">
         <v>10</v>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="20">
         <v>2</v>
       </c>
       <c r="I12" s="1"/>
@@ -5173,33 +5075,18 @@
     <mergeCell ref="B6:H6"/>
   </mergeCells>
   <conditionalFormatting sqref="B21:B109">
-    <cfRule type="expression" dxfId="9" priority="10">
+    <cfRule type="expression" dxfId="2" priority="10">
       <formula>LEN(B21)&gt;120</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11:H11">
-    <cfRule type="expression" dxfId="8" priority="5">
-      <formula>LEN(B11)&gt;120</formula>
+  <conditionalFormatting sqref="B9:H12">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>LEN(B9)&gt;120</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:F109">
-    <cfRule type="expression" dxfId="7" priority="11">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>LEN(C21)&gt;75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12:H12">
-    <cfRule type="expression" dxfId="6" priority="4">
-      <formula>LEN(B12)&gt;120</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10:H10">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>LEN(B10)&gt;120</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9:H9">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>LEN(B9)&gt;120</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>
